--- a/artfynd/A 23345-2026 artfynd.xlsx
+++ b/artfynd/A 23345-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY22"/>
+  <dimension ref="A1:AZ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108260</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108264</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108267</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108270</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108276</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108285</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108287</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1568,6 +1608,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108284</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1687,6 +1732,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108262</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108265</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1925,6 +1980,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108266</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2044,6 +2104,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108275</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2163,6 +2228,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108279</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2297,6 +2367,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108280</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2416,6 +2491,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108282</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2535,6 +2615,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108283</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2654,6 +2739,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108286</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2765,6 +2855,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108272</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2885,6 +2980,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108268</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -3013,6 +3113,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108273</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3137,8 +3242,36 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135108274</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 23345-2026 artfynd.xlsx
+++ b/artfynd/A 23345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135108260</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135108264</v>
       </c>
       <c r="B3" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135108267</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135108270</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135108276</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135108285</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135108287</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1495,7 +1495,7 @@
         <v>135108284</v>
       </c>
       <c r="B9" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1619,7 +1619,7 @@
         <v>135108262</v>
       </c>
       <c r="B10" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>135108265</v>
       </c>
       <c r="B11" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1867,7 +1867,7 @@
         <v>135108266</v>
       </c>
       <c r="B12" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1991,7 +1991,7 @@
         <v>135108275</v>
       </c>
       <c r="B13" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>135108279</v>
       </c>
       <c r="B14" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2239,7 +2239,7 @@
         <v>135108280</v>
       </c>
       <c r="B15" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>135108282</v>
       </c>
       <c r="B16" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2502,7 +2502,7 @@
         <v>135108283</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2626,7 +2626,7 @@
         <v>135108286</v>
       </c>
       <c r="B18" t="n">
-        <v>57975</v>
+        <v>57980</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>135108272</v>
       </c>
       <c r="B19" t="n">
-        <v>111153</v>
+        <v>111210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>135108268</v>
       </c>
       <c r="B20" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135108273</v>
       </c>
       <c r="B21" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>135108274</v>
       </c>
       <c r="B22" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>

--- a/artfynd/A 23345-2026 artfynd.xlsx
+++ b/artfynd/A 23345-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135108260</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135108264</v>
       </c>
       <c r="B3" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135108267</v>
       </c>
       <c r="B4" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135108270</v>
       </c>
       <c r="B5" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135108276</v>
       </c>
       <c r="B6" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1263,7 +1263,7 @@
         <v>135108285</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1379,7 +1379,7 @@
         <v>135108287</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -2750,7 +2750,7 @@
         <v>135108272</v>
       </c>
       <c r="B19" t="n">
-        <v>111210</v>
+        <v>111237</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2866,7 +2866,7 @@
         <v>135108268</v>
       </c>
       <c r="B20" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2991,7 +2991,7 @@
         <v>135108273</v>
       </c>
       <c r="B21" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3124,7 +3124,7 @@
         <v>135108274</v>
       </c>
       <c r="B22" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
